--- a/mode_docx_gen/pmi_lodzt/part/tpbrf/rbrf1/GENRBRF1.xlsx
+++ b/mode_docx_gen/pmi_lodzt/part/tpbrf/rbrf1/GENRBRF1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="111">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>alias</t>
+  </si>
+  <si>
+    <t>Iset</t>
   </si>
 </sst>
 </file>
@@ -1814,6 +1817,9 @@
       <c r="AD11" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="AE11" s="3" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="12" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
@@ -2089,6 +2095,9 @@
       </c>
       <c r="AD14" s="3" t="s">
         <v>32</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
